--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="131">
   <si>
     <t>DateTime</t>
   </si>
@@ -740,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1029"/>
+  <dimension ref="A1:E1042"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14270,6 +14270,194 @@
         <v>90</v>
       </c>
     </row>
+    <row r="1030" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1030" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1030" s="1">
+        <v>46073.5</v>
+      </c>
+      <c r="C1030" s="2">
+        <v>1.86</v>
+      </c>
+      <c r="D1030">
+        <v>0.11</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1031" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1031" s="1">
+        <v>46074.5</v>
+      </c>
+      <c r="C1031" s="2">
+        <v>1.86</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1032" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1032" s="1">
+        <v>46075.5</v>
+      </c>
+      <c r="C1032" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1033" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1033" s="1">
+        <v>46076.5</v>
+      </c>
+      <c r="C1033" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="D1033">
+        <v>0.01</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1034" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1034" s="1">
+        <v>46077.482638888891</v>
+      </c>
+      <c r="C1034" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1035" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1035" s="1">
+        <v>46078.5</v>
+      </c>
+      <c r="C1035" s="2">
+        <v>1.84</v>
+      </c>
+      <c r="D1035">
+        <v>0.12</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1036" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1036" s="1">
+        <v>46079.5</v>
+      </c>
+      <c r="C1036" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="D1036">
+        <v>0.01</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1037" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1037" s="1">
+        <v>46080.606249999997</v>
+      </c>
+      <c r="C1037" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="D1037">
+        <v>0.02</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1038" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1038" s="1">
+        <v>46081.5</v>
+      </c>
+      <c r="C1038" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1039" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1039" s="1">
+        <v>46082.5</v>
+      </c>
+      <c r="C1039" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1040" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1040" s="1">
+        <v>46083.5</v>
+      </c>
+      <c r="C1040" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1041" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1041" s="1">
+        <v>46084.573611111111</v>
+      </c>
+      <c r="C1041" s="2">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1042" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1042" s="1">
+        <v>46085.507638888892</v>
+      </c>
+      <c r="C1042" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="131">
   <si>
     <t>DateTime</t>
   </si>
@@ -740,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1042"/>
+  <dimension ref="A1:E1047"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14436,7 +14436,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
         <v>108</v>
       </c>
@@ -14447,7 +14447,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
         <v>108</v>
       </c>
@@ -14456,6 +14456,70 @@
       </c>
       <c r="C1042" s="2">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1043" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1043" s="1">
+        <v>45721.507638888892</v>
+      </c>
+      <c r="C1043" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1044" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1044" s="1">
+        <v>46087.5</v>
+      </c>
+      <c r="C1044" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1045" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1045" s="1">
+        <v>46088.5</v>
+      </c>
+      <c r="C1045" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="D1045">
+        <v>0.15</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1046" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1046" s="1">
+        <v>46089.541666666664</v>
+      </c>
+      <c r="C1046" s="2">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1047" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1047" s="1">
+        <v>46090.575694444444</v>
+      </c>
+      <c r="C1047" s="2">
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="131">
   <si>
     <t>DateTime</t>
   </si>
@@ -740,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1047"/>
+  <dimension ref="A1:E1055"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14522,6 +14522,121 @@
         <v>1.82</v>
       </c>
     </row>
+    <row r="1048" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1048" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1048" s="1">
+        <v>46091.440972222219</v>
+      </c>
+      <c r="C1048" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="D1048">
+        <v>0.11</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1049" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1049" s="1">
+        <v>46092.59652777778</v>
+      </c>
+      <c r="C1049" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="D1049">
+        <v>0.27</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1050" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1050" s="1">
+        <v>46093.5</v>
+      </c>
+      <c r="C1050" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1051" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1051" s="1">
+        <v>46094.555555555555</v>
+      </c>
+      <c r="C1051" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1051">
+        <v>0.75</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1052" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1052" s="1">
+        <v>46095.4375</v>
+      </c>
+      <c r="C1052" s="2">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1053" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1053" s="1">
+        <v>46096.638888888891</v>
+      </c>
+      <c r="C1053" s="2">
+        <v>1.94</v>
+      </c>
+      <c r="D1053">
+        <v>0.25</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1054" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1054" s="1">
+        <v>46097.479166666664</v>
+      </c>
+      <c r="C1054" s="2">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1055" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1055" s="1">
+        <v>46098.645833333336</v>
+      </c>
+      <c r="C1055" s="2">
+        <v>1.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="131">
   <si>
     <t>DateTime</t>
   </si>
@@ -740,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1055"/>
+  <dimension ref="A1:E1066"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14637,6 +14637,154 @@
         <v>1.92</v>
       </c>
     </row>
+    <row r="1056" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1056" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1056" s="1">
+        <v>46099.5</v>
+      </c>
+      <c r="C1056" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1057" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1057" s="1">
+        <v>46100.611111111109</v>
+      </c>
+      <c r="C1057" s="2">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1058" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1058" s="1">
+        <v>46101.5</v>
+      </c>
+      <c r="C1058" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1059" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1059" s="1">
+        <v>46102.5</v>
+      </c>
+      <c r="C1059" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1059">
+        <v>0.04</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1060" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1060" s="1">
+        <v>46103.5</v>
+      </c>
+      <c r="C1060" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1061" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1061" s="1">
+        <v>46104.5</v>
+      </c>
+      <c r="C1061" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1062" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1062" s="1">
+        <v>46105.5</v>
+      </c>
+      <c r="C1062" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1063" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1063" s="1">
+        <v>46106.481944444444</v>
+      </c>
+      <c r="C1063" s="2">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1064" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1064" s="1">
+        <v>46107.5</v>
+      </c>
+      <c r="C1064" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1065" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1065" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="C1065" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1066" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1066" s="1">
+        <v>46109.602777777778</v>
+      </c>
+      <c r="C1066" s="2">
+        <v>1.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="132">
   <si>
     <t>DateTime</t>
   </si>
@@ -418,6 +418,9 @@
   <si>
     <t>SWE; Extrapolated</t>
   </si>
+  <si>
+    <t>SWE (though some was rain)</t>
+  </si>
 </sst>
 </file>
 
@@ -740,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1066"/>
+  <dimension ref="A1:E1073"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14785,6 +14788,98 @@
         <v>1.87</v>
       </c>
     </row>
+    <row r="1067" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1067" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1067" s="1">
+        <v>46110.479166666664</v>
+      </c>
+      <c r="C1067" s="2">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1068" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1068" s="1">
+        <v>46111.657638888886</v>
+      </c>
+      <c r="C1068" s="2">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1069" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1069" s="1">
+        <v>46112.585416666669</v>
+      </c>
+      <c r="C1069" s="2">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1070" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1070" s="1">
+        <v>46113.568055555559</v>
+      </c>
+      <c r="C1070" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1071" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1071" s="1">
+        <v>46114.5</v>
+      </c>
+      <c r="C1071" s="2">
+        <v>1.84</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1072" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1072" s="1">
+        <v>46115.415277777778</v>
+      </c>
+      <c r="C1072" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="D1072">
+        <v>0.65</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1073" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1073" s="1">
+        <v>46116.560416666667</v>
+      </c>
+      <c r="C1073" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="D1073">
+        <v>0.35</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="134">
   <si>
     <t>DateTime</t>
   </si>
@@ -421,6 +421,12 @@
   <si>
     <t>SWE (though some was rain)</t>
   </si>
+  <si>
+    <t>SWE; Kevin S took measurement</t>
+  </si>
+  <si>
+    <t>Rain; Kevin S took measurement</t>
+  </si>
 </sst>
 </file>
 
@@ -743,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1073"/>
+  <dimension ref="A1:E1083"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14466,7 +14472,7 @@
         <v>108</v>
       </c>
       <c r="B1043" s="1">
-        <v>45721.507638888892</v>
+        <v>46086.507638888892</v>
       </c>
       <c r="C1043" s="2">
         <v>1.8</v>
@@ -14878,6 +14884,158 @@
       </c>
       <c r="E1073" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1074" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1074" s="1">
+        <v>46117.5</v>
+      </c>
+      <c r="C1074" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1075" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1075" s="1">
+        <v>46118.5</v>
+      </c>
+      <c r="C1075" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1075">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1076" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1076" s="1">
+        <v>46119.5</v>
+      </c>
+      <c r="C1076" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1077" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1077" s="1">
+        <v>46120.5</v>
+      </c>
+      <c r="C1077" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1078" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1078" s="1">
+        <v>46121.5</v>
+      </c>
+      <c r="C1078" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1078">
+        <v>0.09</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1079" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1079" s="1">
+        <v>46122.5</v>
+      </c>
+      <c r="C1079" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1080" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1080" s="1">
+        <v>46123.5</v>
+      </c>
+      <c r="C1080" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1081" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1081" s="1">
+        <v>46124.5</v>
+      </c>
+      <c r="C1081" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1081">
+        <v>0.2</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1082" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1082" s="1">
+        <v>46125.5</v>
+      </c>
+      <c r="C1082" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1082">
+        <v>0.02</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1083" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1083" s="1">
+        <v>46126.405555555553</v>
+      </c>
+      <c r="C1083" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="D1083">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="136">
   <si>
     <t>DateTime</t>
   </si>
@@ -427,6 +427,12 @@
   <si>
     <t>Rain; Kevin S took measurement</t>
   </si>
+  <si>
+    <t>Rain; Ice out on Eagle today</t>
+  </si>
+  <si>
+    <t>2026-27</t>
+  </si>
 </sst>
 </file>
 
@@ -749,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1083"/>
+  <dimension ref="A1:E1092"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -15038,6 +15044,111 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="1084" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1084" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1084" s="1">
+        <v>46127.547222222223</v>
+      </c>
+      <c r="C1084" s="2">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1085" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1085" s="1">
+        <v>46128.609027777777</v>
+      </c>
+      <c r="C1085" s="2">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1086" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1086" s="1">
+        <v>46129.546527777777</v>
+      </c>
+      <c r="C1086" s="2">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1087" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1087" s="1">
+        <v>46130.522222222222</v>
+      </c>
+      <c r="C1087" s="2">
+        <v>1.94</v>
+      </c>
+      <c r="D1087">
+        <v>0.36</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1088" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1088" s="1">
+        <v>46131.481249999997</v>
+      </c>
+      <c r="C1088" s="2">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1089" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1089" s="1">
+        <v>46132.396527777775</v>
+      </c>
+      <c r="C1089" s="2">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1090" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1090" s="1">
+        <v>46133.675000000003</v>
+      </c>
+      <c r="C1090" s="2">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1091" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1091" s="1">
+        <v>46134.488194444442</v>
+      </c>
+      <c r="C1091" s="2">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1092" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1092" s="1">
+        <v>46135.561111111114</v>
+      </c>
+      <c r="C1092" s="2">
+        <v>1.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -433,6 +433,24 @@
   <si>
     <t>2026-27</t>
   </si>
+  <si>
+    <t>Suckers spawning above dam</t>
+  </si>
+  <si>
+    <t>No suckers</t>
+  </si>
+  <si>
+    <t>1.98 at 11:17 and 2.00 at 14:49</t>
+  </si>
+  <si>
+    <t>Suckers are back</t>
+  </si>
+  <si>
+    <t>Still some suckers</t>
+  </si>
+  <si>
+    <t>double-checked reading</t>
+  </si>
 </sst>
 </file>
 
@@ -755,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1092"/>
+  <dimension ref="A1:E1129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -15105,7 +15123,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="1089" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1089" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1089" t="s">
         <v>135</v>
       </c>
@@ -15116,7 +15134,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="1090" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1090" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1090" t="s">
         <v>135</v>
       </c>
@@ -15127,7 +15145,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1091" t="s">
         <v>135</v>
       </c>
@@ -15138,7 +15156,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1092" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1092" t="s">
         <v>135</v>
       </c>
@@ -15147,6 +15165,488 @@
       </c>
       <c r="C1092" s="2">
         <v>1.85</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1093" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1093" s="1">
+        <v>46136.345138888886</v>
+      </c>
+      <c r="C1093" s="2">
+        <v>2.06</v>
+      </c>
+      <c r="D1093">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1094" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1094" s="1">
+        <v>46137.5</v>
+      </c>
+      <c r="C1094" s="2">
+        <v>2.02</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1095" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1095" s="1">
+        <v>46138.5</v>
+      </c>
+      <c r="C1095" s="2">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D1095">
+        <v>0.04</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1096" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1096" s="1">
+        <v>46139.510416666664</v>
+      </c>
+      <c r="C1096" s="2">
+        <v>2.02</v>
+      </c>
+      <c r="D1096">
+        <v>0.37</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1097" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1097" s="1">
+        <v>46140.603472222225</v>
+      </c>
+      <c r="C1097" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="D1097">
+        <v>0.68</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1098" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1098" s="1">
+        <v>46141.597222222219</v>
+      </c>
+      <c r="C1098" s="2">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1099" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1099" s="1">
+        <v>46142.543055555558</v>
+      </c>
+      <c r="C1099" s="2">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="D1099">
+        <v>0.03</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1100" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1100" s="1">
+        <v>46143.510416666664</v>
+      </c>
+      <c r="C1100" s="2">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1101" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1101" s="1">
+        <v>46144.525694444441</v>
+      </c>
+      <c r="C1101" s="2">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1102" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1102" s="1">
+        <v>46145.5</v>
+      </c>
+      <c r="C1102" s="2">
+        <v>1.99</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1103" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1103" s="1">
+        <v>46146.511805555558</v>
+      </c>
+      <c r="C1103" s="2">
+        <v>1.99</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1104" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1104" s="1">
+        <v>46147.582638888889</v>
+      </c>
+      <c r="C1104" s="2">
+        <v>1.96</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1105" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1105" s="1">
+        <v>46148.597916666666</v>
+      </c>
+      <c r="C1105" s="2">
+        <v>1.94</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1106" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1106" s="1">
+        <v>46149.531944444447</v>
+      </c>
+      <c r="C1106" s="2">
+        <v>1.94</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1107" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1107" s="1">
+        <v>46150.464583333334</v>
+      </c>
+      <c r="C1107" s="2">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1108" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1108" s="1">
+        <v>46151.557638888888</v>
+      </c>
+      <c r="C1108" s="2">
+        <v>1.95</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1109" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1109" s="1">
+        <v>46152.618055555555</v>
+      </c>
+      <c r="C1109" s="2">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1110" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1110" s="1">
+        <v>46153.576388888891</v>
+      </c>
+      <c r="C1110" s="2">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1111" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1111" s="1">
+        <v>46154.604166666664</v>
+      </c>
+      <c r="C1111" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="D1111">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1112" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1112" s="1">
+        <v>46155.668749999997</v>
+      </c>
+      <c r="C1112" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="D1112">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1113" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1113" s="1">
+        <v>46156.738194444442</v>
+      </c>
+      <c r="C1113" s="2">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1114" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1114" s="1">
+        <v>46157.481944444444</v>
+      </c>
+      <c r="C1114" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="D1114">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1115" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1115" s="1">
+        <v>46158.591666666667</v>
+      </c>
+      <c r="C1115" s="2">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1116" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1116" s="1">
+        <v>46159.484722222223</v>
+      </c>
+      <c r="C1116" s="2">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1117" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1117" s="1">
+        <v>46160.543055555558</v>
+      </c>
+      <c r="C1117" s="2">
+        <v>1.87</v>
+      </c>
+      <c r="D1117">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1118" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1118" s="1">
+        <v>46161.645138888889</v>
+      </c>
+      <c r="C1118" s="2">
+        <v>1.92</v>
+      </c>
+      <c r="D1118">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1119" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1119" s="1">
+        <v>46162.506944444445</v>
+      </c>
+      <c r="C1119" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="D1119">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1120" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1120" s="1">
+        <v>46163.573611111111</v>
+      </c>
+      <c r="C1120" s="2">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1121" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1121" s="1">
+        <v>46164.395833333336</v>
+      </c>
+      <c r="C1121" s="2">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1122" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1122" s="1">
+        <v>46165.592361111114</v>
+      </c>
+      <c r="C1122" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="D1122">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1123" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1123" s="1">
+        <v>46166.554861111108</v>
+      </c>
+      <c r="C1123" s="2">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1124" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1124" s="1">
+        <v>46167.384027777778</v>
+      </c>
+      <c r="C1124" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="D1124">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1125" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1125" s="1">
+        <v>46168.571527777778</v>
+      </c>
+      <c r="C1125" s="2">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1126" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1126" s="1">
+        <v>46169.405555555553</v>
+      </c>
+      <c r="C1126" s="2">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1127" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1127" s="1">
+        <v>46170.428472222222</v>
+      </c>
+      <c r="C1127" s="2">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1128" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1128" s="1">
+        <v>46171.70208333333</v>
+      </c>
+      <c r="C1128" s="2">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1129" s="1">
+        <v>46172.404166666667</v>
+      </c>
+      <c r="C1129" s="2">
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1129"/>
+  <dimension ref="A1:E1138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -15649,6 +15649,114 @@
         <v>1.86</v>
       </c>
     </row>
+    <row r="1130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1130" s="1">
+        <v>46173.470833333333</v>
+      </c>
+      <c r="C1130" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1131" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1131" s="1">
+        <v>46174.59652777778</v>
+      </c>
+      <c r="C1131" s="2">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1132" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1132" s="1">
+        <v>46175.505555555559</v>
+      </c>
+      <c r="C1132" s="2">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1133" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1133" s="1">
+        <v>46176.547222222223</v>
+      </c>
+      <c r="C1133" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1134" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1134" s="1">
+        <v>46177.456250000003</v>
+      </c>
+      <c r="C1134" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1135" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1135" s="1">
+        <v>46178.474999999999</v>
+      </c>
+      <c r="C1135" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1136" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1136" s="1">
+        <v>46179.49722222222</v>
+      </c>
+      <c r="C1136" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="D1136">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1137" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1137" s="1">
+        <v>46180.453472222223</v>
+      </c>
+      <c r="C1137" s="2">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1138" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1138" s="1">
+        <v>46181.423611111109</v>
+      </c>
+      <c r="C1138" s="2">
+        <v>1.86</v>
+      </c>
+      <c r="D1138">
+        <v>0.25</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1138"/>
+  <dimension ref="A1:E1154"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -15757,6 +15757,209 @@
         <v>73</v>
       </c>
     </row>
+    <row r="1139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1139" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1139" s="1">
+        <v>46182.582638888889</v>
+      </c>
+      <c r="C1139" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="D1139">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1140" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1140" s="1">
+        <v>46183.386805555558</v>
+      </c>
+      <c r="C1140" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="D1140">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1141" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1141" s="1">
+        <v>46184.581250000003</v>
+      </c>
+      <c r="C1141" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="D1141">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1142" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1142" s="1">
+        <v>46185.51666666667</v>
+      </c>
+      <c r="C1142" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="D1142">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1143" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1143" s="1">
+        <v>45090.450694444444</v>
+      </c>
+      <c r="C1143" s="2">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1144" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1144" s="1">
+        <v>46187.652083333334</v>
+      </c>
+      <c r="C1144" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1145" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1145" s="1">
+        <v>46188.416666666664</v>
+      </c>
+      <c r="C1145" s="2">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1146" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1146" s="1">
+        <v>46189.595833333333</v>
+      </c>
+      <c r="C1146" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="D1146">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1147" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1147" s="1">
+        <v>46190.68472222222</v>
+      </c>
+      <c r="C1147" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="D1147">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1148" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1148" s="1">
+        <v>46191.508333333331</v>
+      </c>
+      <c r="C1148" s="2">
+        <v>1.86</v>
+      </c>
+      <c r="D1148">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1149" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1149" s="1">
+        <v>46192.570833333331</v>
+      </c>
+      <c r="C1149" s="2">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1150" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1150" s="1">
+        <v>46193.626388888886</v>
+      </c>
+      <c r="C1150" s="2">
+        <v>1.84</v>
+      </c>
+      <c r="D1150">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1151" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1151" s="1">
+        <v>46194.671527777777</v>
+      </c>
+      <c r="C1151" s="2">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1152" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1152" s="1">
+        <v>46195.582638888889</v>
+      </c>
+      <c r="C1152" s="2">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1153" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1153" s="1">
+        <v>46196.584027777775</v>
+      </c>
+      <c r="C1153" s="2">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1154" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1154" s="1">
+        <v>46197.42291666667</v>
+      </c>
+      <c r="C1154" s="2">
+        <v>1.79</v>
+      </c>
+      <c r="D1154">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1154"/>
+  <dimension ref="A1:E1159"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -15935,7 +15935,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1153" t="s">
         <v>135</v>
       </c>
@@ -15946,7 +15946,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1154" t="s">
         <v>135</v>
       </c>
@@ -15958,6 +15958,70 @@
       </c>
       <c r="D1154">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1155" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1155" s="1">
+        <v>46198.430555555555</v>
+      </c>
+      <c r="C1155" s="2">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1156" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1156" s="1">
+        <v>46199.736805555556</v>
+      </c>
+      <c r="C1156" s="2">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1157" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1157" s="1">
+        <v>46200.5</v>
+      </c>
+      <c r="C1157" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1158" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1158" s="1">
+        <v>46201.53402777778</v>
+      </c>
+      <c r="C1158" s="2">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1159" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1159" s="1">
+        <v>46202.615972222222</v>
+      </c>
+      <c r="C1159" s="2">
+        <v>1.76</v>
+      </c>
+      <c r="D1159">
+        <v>0.12</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1159"/>
+  <dimension ref="A1:E1168"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16024,6 +16024,117 @@
         <v>117</v>
       </c>
     </row>
+    <row r="1160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1160" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1160" s="1">
+        <v>46203.369444444441</v>
+      </c>
+      <c r="C1160" s="2">
+        <v>1.85</v>
+      </c>
+      <c r="D1160">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1161" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1161" s="1">
+        <v>46204.589583333334</v>
+      </c>
+      <c r="C1161" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1162" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1162" s="1">
+        <v>46205.429166666669</v>
+      </c>
+      <c r="C1162" s="2">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1163" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1163" s="1">
+        <v>46206.506944444445</v>
+      </c>
+      <c r="C1163" s="2">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1164" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1164" s="1">
+        <v>46207.397916666669</v>
+      </c>
+      <c r="C1164" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="D1164">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1165" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1165" s="1">
+        <v>46208.613194444442</v>
+      </c>
+      <c r="C1165" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1166" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1166" s="1">
+        <v>46209.575694444444</v>
+      </c>
+      <c r="C1166" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1167" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1167" s="1">
+        <v>46210.756944444445</v>
+      </c>
+      <c r="C1167" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="D1167">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1168" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1168" s="1">
+        <v>46211.430555555555</v>
+      </c>
+      <c r="C1168" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="D1168">
+        <v>0.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1168"/>
+  <dimension ref="A1:E1173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16135,6 +16135,61 @@
         <v>0.32</v>
       </c>
     </row>
+    <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1169" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1169" s="1">
+        <v>46212.5</v>
+      </c>
+      <c r="C1169" s="2">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1170" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1170" s="1">
+        <v>46213.487500000003</v>
+      </c>
+      <c r="C1170" s="2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1171" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1171" s="1">
+        <v>46214.576388888891</v>
+      </c>
+      <c r="C1171" s="2">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1172" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1172" s="1">
+        <v>46215.511111111111</v>
+      </c>
+      <c r="C1172" s="2">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1173" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1173" s="1">
+        <v>46216.450694444444</v>
+      </c>
+      <c r="C1173" s="2">
+        <v>1.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1173"/>
+  <dimension ref="A1:E1185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16135,7 +16135,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1169" t="s">
         <v>135</v>
       </c>
@@ -16146,7 +16146,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1170" t="s">
         <v>135</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1171" t="s">
         <v>135</v>
       </c>
@@ -16168,7 +16168,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1172" t="s">
         <v>135</v>
       </c>
@@ -16179,7 +16179,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1173" t="s">
         <v>135</v>
       </c>
@@ -16188,6 +16188,147 @@
       </c>
       <c r="C1173" s="2">
         <v>1.78</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1174" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1174" s="1">
+        <v>46217.404166666667</v>
+      </c>
+      <c r="C1174" s="2">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1175" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1175" s="1">
+        <v>46218.417361111111</v>
+      </c>
+      <c r="C1175" s="2">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1176" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1176" s="1">
+        <v>46219.5</v>
+      </c>
+      <c r="C1176" s="2">
+        <v>1.73</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1177" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1177" s="1">
+        <v>46220.649305555555</v>
+      </c>
+      <c r="C1177" s="2">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1178" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1178" s="1">
+        <v>46221.416666666664</v>
+      </c>
+      <c r="C1178" s="2">
+        <v>1.74</v>
+      </c>
+      <c r="D1178">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1179" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1179" s="1">
+        <v>46222.663194444445</v>
+      </c>
+      <c r="C1179" s="2">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1180" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1180" s="1">
+        <v>46223.418749999997</v>
+      </c>
+      <c r="C1180" s="2">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1181" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1181" s="1">
+        <v>46224.67291666667</v>
+      </c>
+      <c r="C1181" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="D1181">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1182" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1182" s="1">
+        <v>46225.413888888892</v>
+      </c>
+      <c r="C1182" s="2">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1183" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1183" s="1">
+        <v>46226.45208333333</v>
+      </c>
+      <c r="C1183" s="2">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1184" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1184" s="1">
+        <v>46227.506944444445</v>
+      </c>
+      <c r="C1184" s="2">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1185" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1185" s="1">
+        <v>46228.508333333331</v>
+      </c>
+      <c r="C1185" s="2">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="142">
   <si>
     <t>DateTime</t>
   </si>
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1185"/>
+  <dimension ref="A1:E1190"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16331,6 +16331,61 @@
         <v>1.64</v>
       </c>
     </row>
+    <row r="1186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1186" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1186" s="1">
+        <v>46229.594444444447</v>
+      </c>
+      <c r="C1186" s="2">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1187" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1187" s="1">
+        <v>46230.679861111108</v>
+      </c>
+      <c r="C1187" s="2">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1188" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1188" s="1">
+        <v>46231.438194444447</v>
+      </c>
+      <c r="C1188" s="2">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1189" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1189" s="1">
+        <v>46232.460416666669</v>
+      </c>
+      <c r="C1189" s="2">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1190" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1190" s="1">
+        <v>46233.399305555555</v>
+      </c>
+      <c r="C1190" s="2">
+        <v>1.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="144">
   <si>
     <t>DateTime</t>
   </si>
@@ -451,6 +451,12 @@
   <si>
     <t>double-checked reading</t>
   </si>
+  <si>
+    <t>Measurement soon after rain ended</t>
+  </si>
+  <si>
+    <t>Cleaned weeds and some sticks off grate</t>
+  </si>
 </sst>
 </file>
 
@@ -773,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1190"/>
+  <dimension ref="A1:E1198"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16320,7 +16326,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="1185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1185" t="s">
         <v>135</v>
       </c>
@@ -16331,7 +16337,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="1186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1186" t="s">
         <v>135</v>
       </c>
@@ -16341,8 +16347,11 @@
       <c r="C1186" s="2">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="1187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E1186" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1187" t="s">
         <v>135</v>
       </c>
@@ -16353,7 +16362,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="1188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1188" t="s">
         <v>135</v>
       </c>
@@ -16364,7 +16373,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="1189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1189" t="s">
         <v>135</v>
       </c>
@@ -16375,7 +16384,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="1190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1190" t="s">
         <v>135</v>
       </c>
@@ -16384,6 +16393,103 @@
       </c>
       <c r="C1190" s="2">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1191" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1191" s="1">
+        <v>46234.651388888888</v>
+      </c>
+      <c r="C1191" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="D1191">
+        <v>0.36</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1192" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1192" s="1">
+        <v>46235.702777777777</v>
+      </c>
+      <c r="C1192" s="2">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1193" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1193" s="1">
+        <v>46236.695833333331</v>
+      </c>
+      <c r="C1193" s="2">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1194" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1194" s="1">
+        <v>46237.381249999999</v>
+      </c>
+      <c r="C1194" s="2">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1195" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1195" s="1">
+        <v>46238.462500000001</v>
+      </c>
+      <c r="C1195" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="D1195">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1196" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1196" s="1">
+        <v>46239.654861111114</v>
+      </c>
+      <c r="C1196" s="2">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1197" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1197" s="1">
+        <v>46240.395138888889</v>
+      </c>
+      <c r="C1197" s="2">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1198" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1198" s="1">
+        <v>46241.430555555555</v>
+      </c>
+      <c r="C1198" s="2">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>
